--- a/outputs/master_rename_build/tables/stepA_empty_rungs.xlsx
+++ b/outputs/master_rename_build/tables/stepA_empty_rungs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1605" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1623" uniqueCount="138">
   <si>
     <t>pull_item</t>
   </si>
@@ -39,18 +39,21 @@
     <t>crackers, cookies, buiscuits, chips/curls</t>
   </si>
   <si>
+    <t>cabbage</t>
+  </si>
+  <si>
     <t>drinks at restaurant, hotel, cafe, or kiosk</t>
   </si>
   <si>
     <t>camote</t>
   </si>
   <si>
-    <t>cabbage</t>
-  </si>
-  <si>
     <t>prawns, lobster, shrimp</t>
   </si>
   <si>
+    <t>carrot</t>
+  </si>
+  <si>
     <t>pull_province</t>
   </si>
   <si>
@@ -198,6 +201,9 @@
     <t>TAPAZ</t>
   </si>
   <si>
+    <t>AJUY</t>
+  </si>
+  <si>
     <t>ALIMODIAN</t>
   </si>
   <si>
@@ -333,6 +339,9 @@
     <t>PULUPANDAN</t>
   </si>
   <si>
+    <t>VALLADOLID</t>
+  </si>
+  <si>
     <t>harmonized_nsu_unit</t>
   </si>
   <si>
@@ -375,15 +384,15 @@
     <t>cone</t>
   </si>
   <si>
+    <t>pack</t>
+  </si>
+  <si>
     <t>junior lapad</t>
   </si>
   <si>
     <t>pieces</t>
   </si>
   <si>
-    <t>pack</t>
-  </si>
-  <si>
     <t>cans</t>
   </si>
   <si>
@@ -415,6 +424,9 @@
   </si>
   <si>
     <t>size</t>
+  </si>
+  <si>
+    <t>price</t>
   </si>
 </sst>
 </file>
@@ -460,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I267"/>
+  <dimension ref="A1:I270"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,28 +480,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2">
@@ -497,16 +509,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F2" s="1">
         <v>3</v>
@@ -518,7 +530,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
@@ -526,16 +538,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F3" s="1">
         <v>4</v>
@@ -547,7 +559,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4">
@@ -555,16 +567,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F4" s="1">
         <v>4</v>
@@ -576,7 +588,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
@@ -584,16 +596,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F5" s="1">
         <v>6</v>
@@ -605,7 +617,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6">
@@ -613,16 +625,16 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F6" s="1">
         <v>7</v>
@@ -634,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
@@ -642,16 +654,16 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -663,7 +675,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8">
@@ -671,16 +683,16 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F8" s="1">
         <v>5</v>
@@ -692,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9">
@@ -700,16 +712,16 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F9" s="1">
         <v>9</v>
@@ -721,7 +733,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
@@ -729,16 +741,16 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F10" s="1">
         <v>9</v>
@@ -750,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -758,16 +770,16 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F11" s="1">
         <v>3</v>
@@ -779,7 +791,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -787,16 +799,16 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F12" s="1">
         <v>3</v>
@@ -808,7 +820,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -816,16 +828,16 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F13" s="1">
         <v>3</v>
@@ -837,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -845,16 +857,16 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -866,7 +878,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -874,16 +886,16 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F15" s="1">
         <v>6</v>
@@ -895,7 +907,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16">
@@ -903,16 +915,16 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E16" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1">
         <v>7</v>
@@ -924,7 +936,7 @@
         <v>2</v>
       </c>
       <c r="I16" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17">
@@ -932,16 +944,16 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F17" s="1">
         <v>5</v>
@@ -953,7 +965,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18">
@@ -961,16 +973,16 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F18" s="1">
         <v>7</v>
@@ -982,7 +994,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
@@ -990,16 +1002,16 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F19" s="1">
         <v>6</v>
@@ -1011,7 +1023,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20">
@@ -1019,16 +1031,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F20" s="1">
         <v>5</v>
@@ -1040,7 +1052,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21">
@@ -1048,16 +1060,16 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F21" s="1">
         <v>9</v>
@@ -1069,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22">
@@ -1077,16 +1089,16 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F22" s="1">
         <v>9</v>
@@ -1098,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23">
@@ -1106,16 +1118,16 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F23" s="1">
         <v>9</v>
@@ -1127,7 +1139,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24">
@@ -1135,16 +1147,16 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F24" s="1">
         <v>9</v>
@@ -1156,7 +1168,7 @@
         <v>2</v>
       </c>
       <c r="I24" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25">
@@ -1164,16 +1176,16 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F25" s="1">
         <v>3</v>
@@ -1185,7 +1197,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26">
@@ -1193,16 +1205,16 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E26" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F26" s="1">
         <v>3</v>
@@ -1214,7 +1226,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27">
@@ -1222,16 +1234,16 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F27" s="1">
         <v>6</v>
@@ -1243,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28">
@@ -1251,16 +1263,16 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E28" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F28" s="1">
         <v>6</v>
@@ -1272,7 +1284,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
@@ -1280,16 +1292,16 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E29" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F29" s="1">
         <v>4</v>
@@ -1301,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30">
@@ -1309,16 +1321,16 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E30" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F30" s="1">
         <v>3</v>
@@ -1330,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31">
@@ -1338,16 +1350,16 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F31" s="1">
         <v>10</v>
@@ -1359,7 +1371,7 @@
         <v>2</v>
       </c>
       <c r="I31" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32">
@@ -1367,16 +1379,16 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F32" s="1">
         <v>7</v>
@@ -1388,7 +1400,7 @@
         <v>2</v>
       </c>
       <c r="I32" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33">
@@ -1396,16 +1408,16 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E33" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F33" s="1">
         <v>9</v>
@@ -1417,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34">
@@ -1425,16 +1437,16 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E34" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F34" s="1">
         <v>11</v>
@@ -1446,7 +1458,7 @@
         <v>2</v>
       </c>
       <c r="I34" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35">
@@ -1454,16 +1466,16 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F35" s="1">
         <v>5</v>
@@ -1475,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36">
@@ -1483,16 +1495,16 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E36" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F36" s="1">
         <v>6</v>
@@ -1504,7 +1516,7 @@
         <v>2</v>
       </c>
       <c r="I36" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37">
@@ -1512,16 +1524,16 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E37" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F37" s="1">
         <v>4</v>
@@ -1533,7 +1545,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38">
@@ -1541,16 +1553,16 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E38" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F38" s="1">
         <v>5</v>
@@ -1562,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39">
@@ -1570,16 +1582,16 @@
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E39" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F39" s="1">
         <v>3</v>
@@ -1591,7 +1603,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40">
@@ -1599,16 +1611,16 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D40" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E40" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F40" s="1">
         <v>4</v>
@@ -1620,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41">
@@ -1628,16 +1640,16 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E41" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F41" s="1">
         <v>6</v>
@@ -1649,7 +1661,7 @@
         <v>2</v>
       </c>
       <c r="I41" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42">
@@ -1657,16 +1669,16 @@
         <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E42" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F42" s="1">
         <v>3</v>
@@ -1678,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43">
@@ -1686,16 +1698,16 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E43" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F43" s="1">
         <v>6</v>
@@ -1707,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44">
@@ -1715,16 +1727,16 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E44" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F44" s="1">
         <v>10</v>
@@ -1736,7 +1748,7 @@
         <v>2</v>
       </c>
       <c r="I44" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45">
@@ -1744,16 +1756,16 @@
         <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E45" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F45" s="1">
         <v>7</v>
@@ -1765,7 +1777,7 @@
         <v>2</v>
       </c>
       <c r="I45" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46">
@@ -1773,16 +1785,16 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D46" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E46" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F46" s="1">
         <v>6</v>
@@ -1794,7 +1806,7 @@
         <v>2</v>
       </c>
       <c r="I46" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47">
@@ -1802,16 +1814,16 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E47" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F47" s="1">
         <v>8</v>
@@ -1823,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48">
@@ -1831,16 +1843,16 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D48" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E48" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F48" s="1">
         <v>8</v>
@@ -1852,7 +1864,7 @@
         <v>2</v>
       </c>
       <c r="I48" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49">
@@ -1860,16 +1872,16 @@
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D49" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E49" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F49" s="1">
         <v>3</v>
@@ -1881,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50">
@@ -1889,16 +1901,16 @@
         <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E50" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F50" s="1">
         <v>3</v>
@@ -1910,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51">
@@ -1918,16 +1930,16 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D51" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E51" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F51" s="1">
         <v>11</v>
@@ -1939,7 +1951,7 @@
         <v>2</v>
       </c>
       <c r="I51" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52">
@@ -1947,16 +1959,16 @@
         <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C52" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D52" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E52" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F52" s="1">
         <v>5</v>
@@ -1968,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53">
@@ -1976,16 +1988,16 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D53" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E53" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F53" s="1">
         <v>4</v>
@@ -1997,7 +2009,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54">
@@ -2005,16 +2017,16 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D54" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E54" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F54" s="1">
         <v>7</v>
@@ -2026,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55">
@@ -2034,16 +2046,16 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E55" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F55" s="1">
         <v>7</v>
@@ -2055,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56">
@@ -2063,16 +2075,16 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D56" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E56" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F56" s="1">
         <v>3</v>
@@ -2084,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57">
@@ -2092,16 +2104,16 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D57" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E57" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F57" s="1">
         <v>3</v>
@@ -2113,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58">
@@ -2121,16 +2133,16 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E58" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F58" s="1">
         <v>4</v>
@@ -2142,7 +2154,7 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59">
@@ -2150,16 +2162,16 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D59" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E59" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F59" s="1">
         <v>4</v>
@@ -2171,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60">
@@ -2179,16 +2191,16 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D60" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E60" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F60" s="1">
         <v>6</v>
@@ -2200,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61">
@@ -2208,16 +2220,16 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C61" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D61" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E61" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F61" s="1">
         <v>6</v>
@@ -2229,7 +2241,7 @@
         <v>2</v>
       </c>
       <c r="I61" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62">
@@ -2237,16 +2249,16 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C62" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D62" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E62" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F62" s="1">
         <v>7</v>
@@ -2258,7 +2270,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63">
@@ -2266,16 +2278,16 @@
         <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C63" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E63" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F63" s="1">
         <v>7</v>
@@ -2287,7 +2299,7 @@
         <v>2</v>
       </c>
       <c r="I63" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64">
@@ -2295,16 +2307,16 @@
         <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C64" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D64" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E64" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F64" s="1">
         <v>3</v>
@@ -2316,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65">
@@ -2324,16 +2336,16 @@
         <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C65" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D65" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E65" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F65" s="1">
         <v>3</v>
@@ -2345,7 +2357,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66">
@@ -2353,16 +2365,16 @@
         <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D66" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E66" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F66" s="1">
         <v>3</v>
@@ -2374,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67">
@@ -2382,16 +2394,16 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D67" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E67" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F67" s="1">
         <v>8</v>
@@ -2403,7 +2415,7 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68">
@@ -2411,16 +2423,16 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D68" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E68" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F68" s="1">
         <v>8</v>
@@ -2432,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69">
@@ -2440,16 +2452,16 @@
         <v>1</v>
       </c>
       <c r="B69" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D69" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E69" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F69" s="1">
         <v>5</v>
@@ -2461,7 +2473,7 @@
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70">
@@ -2469,16 +2481,16 @@
         <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C70" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E70" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F70" s="1">
         <v>5</v>
@@ -2490,7 +2502,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71">
@@ -2498,16 +2510,16 @@
         <v>1</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C71" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E71" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F71" s="1">
         <v>9</v>
@@ -2519,7 +2531,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72">
@@ -2527,16 +2539,16 @@
         <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E72" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F72" s="1">
         <v>9</v>
@@ -2548,7 +2560,7 @@
         <v>2</v>
       </c>
       <c r="I72" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73">
@@ -2556,16 +2568,16 @@
         <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C73" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E73" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F73" s="1">
         <v>7</v>
@@ -2577,7 +2589,7 @@
         <v>2</v>
       </c>
       <c r="I73" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74">
@@ -2585,16 +2597,16 @@
         <v>3</v>
       </c>
       <c r="B74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C74" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D74" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E74" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F74" s="1">
         <v>5</v>
@@ -2606,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75">
@@ -2614,16 +2626,16 @@
         <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D75" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E75" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F75" s="1">
         <v>6</v>
@@ -2635,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="I75" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76">
@@ -2643,16 +2655,16 @@
         <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D76" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E76" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F76" s="1">
         <v>6</v>
@@ -2664,7 +2676,7 @@
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77">
@@ -2672,16 +2684,16 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C77" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D77" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F77" s="1">
         <v>6</v>
@@ -2693,7 +2705,7 @@
         <v>2</v>
       </c>
       <c r="I77" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78">
@@ -2701,16 +2713,16 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D78" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E78" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F78" s="1">
         <v>3</v>
@@ -2722,7 +2734,7 @@
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79">
@@ -2730,16 +2742,16 @@
         <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C79" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D79" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E79" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F79" s="1">
         <v>8</v>
@@ -2751,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="I79" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80">
@@ -2759,16 +2771,16 @@
         <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C80" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D80" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E80" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F80" s="1">
         <v>10</v>
@@ -2780,7 +2792,7 @@
         <v>2</v>
       </c>
       <c r="I80" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="81">
@@ -2788,16 +2800,16 @@
         <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C81" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D81" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E81" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F81" s="1">
         <v>7</v>
@@ -2809,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="82">
@@ -2817,16 +2829,16 @@
         <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C82" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D82" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E82" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F82" s="1">
         <v>14</v>
@@ -2838,7 +2850,7 @@
         <v>2</v>
       </c>
       <c r="I82" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="83">
@@ -2846,16 +2858,16 @@
         <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C83" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D83" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E83" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F83" s="1">
         <v>4</v>
@@ -2867,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="I83" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="84">
@@ -2875,16 +2887,16 @@
         <v>2</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C84" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D84" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E84" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F84" s="1">
         <v>5</v>
@@ -2896,7 +2908,7 @@
         <v>1</v>
       </c>
       <c r="I84" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="85">
@@ -2904,16 +2916,16 @@
         <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C85" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D85" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E85" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F85" s="1">
         <v>5</v>
@@ -2925,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="I85" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="86">
@@ -2933,16 +2945,16 @@
         <v>3</v>
       </c>
       <c r="B86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C86" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D86" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E86" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F86" s="1">
         <v>3</v>
@@ -2954,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="I86" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="87">
@@ -2962,16 +2974,16 @@
         <v>3</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C87" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D87" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E87" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F87" s="1">
         <v>7</v>
@@ -2983,7 +2995,7 @@
         <v>2</v>
       </c>
       <c r="I87" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="88">
@@ -2991,16 +3003,16 @@
         <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C88" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E88" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F88" s="1">
         <v>3</v>
@@ -3012,7 +3024,7 @@
         <v>1</v>
       </c>
       <c r="I88" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="89">
@@ -3020,16 +3032,16 @@
         <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C89" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D89" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E89" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F89" s="1">
         <v>3</v>
@@ -3041,7 +3053,7 @@
         <v>1</v>
       </c>
       <c r="I89" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="90">
@@ -3049,16 +3061,16 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C90" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D90" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E90" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F90" s="1">
         <v>3</v>
@@ -3070,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="I90" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="91">
@@ -3078,16 +3090,16 @@
         <v>1</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D91" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E91" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F91" s="1">
         <v>4</v>
@@ -3099,7 +3111,7 @@
         <v>1</v>
       </c>
       <c r="I91" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="92">
@@ -3107,16 +3119,16 @@
         <v>2</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C92" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D92" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E92" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F92" s="1">
         <v>3</v>
@@ -3128,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="I92" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="93">
@@ -3136,16 +3148,16 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D93" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E93" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F93" s="1">
         <v>4</v>
@@ -3157,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="I93" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="94">
@@ -3165,16 +3177,16 @@
         <v>3</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D94" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E94" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F94" s="1">
         <v>3</v>
@@ -3186,7 +3198,7 @@
         <v>1</v>
       </c>
       <c r="I94" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="95">
@@ -3194,16 +3206,16 @@
         <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C95" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D95" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E95" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F95" s="1">
         <v>5</v>
@@ -3215,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="I95" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="96">
@@ -3223,16 +3235,16 @@
         <v>1</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C96" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D96" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E96" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F96" s="1">
         <v>6</v>
@@ -3244,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="I96" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="97">
@@ -3252,16 +3264,16 @@
         <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C97" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D97" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E97" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F97" s="1">
         <v>6</v>
@@ -3273,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="I97" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="98">
@@ -3281,16 +3293,16 @@
         <v>2</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C98" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D98" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E98" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F98" s="1">
         <v>3</v>
@@ -3302,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="I98" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="99">
@@ -3310,16 +3322,16 @@
         <v>2</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C99" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D99" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E99" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F99" s="1">
         <v>3</v>
@@ -3331,7 +3343,7 @@
         <v>1</v>
       </c>
       <c r="I99" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="100">
@@ -3339,16 +3351,16 @@
         <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D100" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E100" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F100" s="1">
         <v>11</v>
@@ -3360,7 +3372,7 @@
         <v>2</v>
       </c>
       <c r="I100" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="101">
@@ -3368,16 +3380,16 @@
         <v>3</v>
       </c>
       <c r="B101" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C101" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D101" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E101" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F101" s="1">
         <v>6</v>
@@ -3389,7 +3401,7 @@
         <v>1</v>
       </c>
       <c r="I101" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="102">
@@ -3397,16 +3409,16 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C102" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D102" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E102" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F102" s="1">
         <v>16</v>
@@ -3418,7 +3430,7 @@
         <v>2</v>
       </c>
       <c r="I102" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="103">
@@ -3426,16 +3438,16 @@
         <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C103" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D103" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E103" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F103" s="1">
         <v>11</v>
@@ -3447,7 +3459,7 @@
         <v>2</v>
       </c>
       <c r="I103" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="104">
@@ -3455,16 +3467,16 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C104" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D104" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E104" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F104" s="1">
         <v>3</v>
@@ -3476,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="I104" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="105">
@@ -3484,16 +3496,16 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C105" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D105" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E105" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F105" s="1">
         <v>6</v>
@@ -3505,7 +3517,7 @@
         <v>2</v>
       </c>
       <c r="I105" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106">
@@ -3513,16 +3525,16 @@
         <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C106" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D106" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E106" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F106" s="1">
         <v>6</v>
@@ -3534,7 +3546,7 @@
         <v>1</v>
       </c>
       <c r="I106" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="107">
@@ -3542,16 +3554,16 @@
         <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C107" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D107" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E107" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F107" s="1">
         <v>5</v>
@@ -3563,7 +3575,7 @@
         <v>1</v>
       </c>
       <c r="I107" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="108">
@@ -3571,16 +3583,16 @@
         <v>2</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C108" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D108" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E108" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F108" s="1">
         <v>3</v>
@@ -3592,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="I108" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="109">
@@ -3600,16 +3612,16 @@
         <v>6</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C109" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D109" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E109" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F109" s="1">
         <v>4</v>
@@ -3621,7 +3633,7 @@
         <v>1</v>
       </c>
       <c r="I109" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="110">
@@ -3629,16 +3641,16 @@
         <v>4</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C110" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D110" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E110" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F110" s="1">
         <v>3</v>
@@ -3650,7 +3662,7 @@
         <v>1</v>
       </c>
       <c r="I110" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="111">
@@ -3658,16 +3670,16 @@
         <v>1</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C111" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D111" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E111" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F111" s="1">
         <v>13</v>
@@ -3679,27 +3691,27 @@
         <v>2</v>
       </c>
       <c r="I111" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D112" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="E112" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F112" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G112" s="1">
         <v>2</v>
@@ -3708,7 +3720,7 @@
         <v>1</v>
       </c>
       <c r="I112" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="113">
@@ -3716,16 +3728,16 @@
         <v>4</v>
       </c>
       <c r="B113" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D113" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E113" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F113" s="1">
         <v>3</v>
@@ -3737,36 +3749,36 @@
         <v>1</v>
       </c>
       <c r="I113" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B114" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D114" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E114" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F114" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G114" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H114" s="1">
         <v>1</v>
       </c>
       <c r="I114" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="115">
@@ -3774,16 +3786,16 @@
         <v>1</v>
       </c>
       <c r="B115" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D115" t="s">
         <v>110</v>
       </c>
       <c r="E115" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F115" s="1">
         <v>9</v>
@@ -3795,94 +3807,94 @@
         <v>1</v>
       </c>
       <c r="I115" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D116" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E116" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F116" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G116" s="1">
         <v>3</v>
       </c>
       <c r="H116" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I116" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B117" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C117" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D117" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E117" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F117" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G117" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H117" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I117" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C118" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D118" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E118" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F118" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G118" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H118" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I118" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="119">
@@ -3890,28 +3902,28 @@
         <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D119" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E119" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F119" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G119" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H119" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I119" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="120">
@@ -3919,16 +3931,16 @@
         <v>1</v>
       </c>
       <c r="B120" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C120" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D120" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E120" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F120" s="1">
         <v>3</v>
@@ -3940,27 +3952,27 @@
         <v>1</v>
       </c>
       <c r="I120" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B121" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C121" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D121" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E121" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F121" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G121" s="1">
         <v>2</v>
@@ -3969,65 +3981,65 @@
         <v>1</v>
       </c>
       <c r="I121" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B122" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C122" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D122" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E122" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F122" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G122" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H122" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I122" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B123" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123" t="s">
+        <v>66</v>
+      </c>
+      <c r="D123" t="s">
+        <v>125</v>
+      </c>
+      <c r="E123" t="s">
+        <v>130</v>
+      </c>
+      <c r="F123" s="1">
         <v>16</v>
       </c>
-      <c r="C123" t="s">
-        <v>64</v>
-      </c>
-      <c r="D123" t="s">
-        <v>107</v>
-      </c>
-      <c r="E123" t="s">
-        <v>127</v>
-      </c>
-      <c r="F123" s="1">
-        <v>6</v>
-      </c>
       <c r="G123" s="1">
         <v>3</v>
       </c>
       <c r="H123" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I123" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="124">
@@ -4035,222 +4047,222 @@
         <v>1</v>
       </c>
       <c r="B124" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C124" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D124" t="s">
         <v>110</v>
       </c>
       <c r="E124" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F124" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G124" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H124" s="1">
         <v>1</v>
       </c>
       <c r="I124" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C125" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D125" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E125" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F125" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G125" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H125" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I125" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B126" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C126" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D126" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E126" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F126" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G126" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H126" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I126" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C127" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D127" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E127" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F127" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G127" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H127" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I127" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C128" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D128" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E128" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F128" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G128" s="1">
         <v>3</v>
       </c>
       <c r="H128" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I128" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B129" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C129" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D129" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E129" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F129" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G129" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H129" s="1">
         <v>1</v>
       </c>
       <c r="I129" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B130" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C130" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D130" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E130" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F130" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G130" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H130" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I130" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B131" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C131" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D131" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E131" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F131" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G131" s="1">
         <v>3</v>
@@ -4259,36 +4271,36 @@
         <v>2</v>
       </c>
       <c r="I131" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B132" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C132" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D132" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E132" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F132" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G132" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H132" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I132" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="133">
@@ -4296,57 +4308,57 @@
         <v>1</v>
       </c>
       <c r="B133" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C133" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D133" t="s">
         <v>110</v>
       </c>
       <c r="E133" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F133" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G133" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H133" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I133" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C134" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D134" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E134" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F134" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G134" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H134" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I134" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="135">
@@ -4354,86 +4366,86 @@
         <v>2</v>
       </c>
       <c r="B135" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C135" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D135" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E135" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F135" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G135" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H135" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I135" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B136" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C136" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D136" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E136" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F136" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G136" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H136" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I136" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B137" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C137" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D137" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E137" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F137" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G137" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H137" s="1">
         <v>1</v>
       </c>
       <c r="I137" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="138">
@@ -4441,48 +4453,48 @@
         <v>1</v>
       </c>
       <c r="B138" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C138" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D138" t="s">
         <v>110</v>
       </c>
       <c r="E138" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F138" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G138" s="1">
         <v>3</v>
       </c>
       <c r="H138" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I138" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B139" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C139" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D139" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E139" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F139" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G139" s="1">
         <v>3</v>
@@ -4491,7 +4503,7 @@
         <v>2</v>
       </c>
       <c r="I139" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="140">
@@ -4499,19 +4511,19 @@
         <v>2</v>
       </c>
       <c r="B140" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C140" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D140" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E140" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F140" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G140" s="1">
         <v>3</v>
@@ -4520,53 +4532,53 @@
         <v>2</v>
       </c>
       <c r="I140" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B141" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C141" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D141" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E141" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F141" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G141" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H141" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I141" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B142" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C142" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D142" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E142" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F142" s="1">
         <v>4</v>
@@ -4578,7 +4590,7 @@
         <v>1</v>
       </c>
       <c r="I142" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="143">
@@ -4586,16 +4598,16 @@
         <v>1</v>
       </c>
       <c r="B143" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C143" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D143" t="s">
         <v>110</v>
       </c>
       <c r="E143" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F143" s="1">
         <v>4</v>
@@ -4607,85 +4619,85 @@
         <v>1</v>
       </c>
       <c r="I143" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
+        <v>1</v>
+      </c>
+      <c r="B144" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" t="s">
+        <v>73</v>
+      </c>
+      <c r="D144" t="s">
+        <v>113</v>
+      </c>
+      <c r="E144" t="s">
+        <v>130</v>
+      </c>
+      <c r="F144" s="1">
         <v>4</v>
       </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="s">
-        <v>72</v>
-      </c>
-      <c r="D144" t="s">
-        <v>112</v>
-      </c>
-      <c r="E144" t="s">
-        <v>127</v>
-      </c>
-      <c r="F144" s="1">
-        <v>7</v>
-      </c>
       <c r="G144" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H144" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I144" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B145" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C145" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D145" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E145" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F145" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G145" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H145" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I145" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B146" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C146" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D146" t="s">
         <v>119</v>
       </c>
       <c r="E146" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F146" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G146" s="1">
         <v>2</v>
@@ -4694,24 +4706,24 @@
         <v>1</v>
       </c>
       <c r="I146" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B147" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C147" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D147" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E147" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F147" s="1">
         <v>5</v>
@@ -4723,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="I147" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="148">
@@ -4731,28 +4743,28 @@
         <v>1</v>
       </c>
       <c r="B148" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C148" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D148" t="s">
         <v>110</v>
       </c>
       <c r="E148" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F148" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G148" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H148" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I148" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="149">
@@ -4760,28 +4772,28 @@
         <v>1</v>
       </c>
       <c r="B149" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C149" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D149" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E149" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F149" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G149" s="1">
         <v>3</v>
       </c>
       <c r="H149" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I149" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="150">
@@ -4789,57 +4801,57 @@
         <v>1</v>
       </c>
       <c r="B150" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C150" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D150" t="s">
         <v>110</v>
       </c>
       <c r="E150" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F150" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G150" s="1">
         <v>3</v>
       </c>
       <c r="H150" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I150" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B151" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C151" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D151" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E151" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F151" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G151" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H151" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I151" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="152">
@@ -4847,16 +4859,16 @@
         <v>3</v>
       </c>
       <c r="B152" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C152" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D152" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E152" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F152" s="1">
         <v>5</v>
@@ -4868,27 +4880,27 @@
         <v>1</v>
       </c>
       <c r="I152" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B153" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C153" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D153" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E153" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F153" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G153" s="1">
         <v>2</v>
@@ -4897,7 +4909,7 @@
         <v>1</v>
       </c>
       <c r="I153" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="154">
@@ -4905,16 +4917,16 @@
         <v>4</v>
       </c>
       <c r="B154" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C154" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D154" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="E154" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F154" s="1">
         <v>3</v>
@@ -4926,7 +4938,7 @@
         <v>1</v>
       </c>
       <c r="I154" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="155">
@@ -4934,16 +4946,16 @@
         <v>4</v>
       </c>
       <c r="B155" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C155" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D155" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E155" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F155" s="1">
         <v>3</v>
@@ -4955,65 +4967,65 @@
         <v>1</v>
       </c>
       <c r="I155" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B156" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C156" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D156" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E156" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F156" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G156" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H156" s="1">
         <v>1</v>
       </c>
       <c r="I156" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B157" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C157" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D157" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E157" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F157" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G157" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H157" s="1">
         <v>1</v>
       </c>
       <c r="I157" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="158">
@@ -5021,16 +5033,16 @@
         <v>2</v>
       </c>
       <c r="B158" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C158" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D158" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E158" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F158" s="1">
         <v>3</v>
@@ -5042,56 +5054,56 @@
         <v>1</v>
       </c>
       <c r="I158" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B159" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C159" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D159" t="s">
         <v>112</v>
       </c>
       <c r="E159" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F159" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G159" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H159" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I159" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B160" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C160" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D160" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E160" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F160" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G160" s="1">
         <v>3</v>
@@ -5100,56 +5112,56 @@
         <v>2</v>
       </c>
       <c r="I160" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B161" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C161" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D161" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E161" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F161" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G161" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H161" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I161" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B162" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C162" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D162" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E162" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F162" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G162" s="1">
         <v>2</v>
@@ -5158,36 +5170,36 @@
         <v>1</v>
       </c>
       <c r="I162" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B163" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C163" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D163" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E163" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F163" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G163" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H163" s="1">
         <v>1</v>
       </c>
       <c r="I163" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="164">
@@ -5195,19 +5207,19 @@
         <v>1</v>
       </c>
       <c r="B164" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C164" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D164" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E164" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F164" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G164" s="1">
         <v>3</v>
@@ -5216,7 +5228,7 @@
         <v>1</v>
       </c>
       <c r="I164" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="165">
@@ -5224,16 +5236,16 @@
         <v>1</v>
       </c>
       <c r="B165" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C165" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D165" t="s">
         <v>110</v>
       </c>
       <c r="E165" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F165" s="1">
         <v>7</v>
@@ -5245,65 +5257,65 @@
         <v>1</v>
       </c>
       <c r="I165" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B166" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C166" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D166" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E166" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F166" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G166" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H166" s="1">
         <v>1</v>
       </c>
       <c r="I166" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B167" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C167" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D167" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E167" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F167" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G167" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H167" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I167" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="168">
@@ -5311,19 +5323,19 @@
         <v>3</v>
       </c>
       <c r="B168" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C168" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D168" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E168" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F168" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G168" s="1">
         <v>3</v>
@@ -5332,65 +5344,65 @@
         <v>2</v>
       </c>
       <c r="I168" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B169" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C169" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D169" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E169" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F169" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G169" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H169" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I169" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B170" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C170" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D170" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E170" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F170" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G170" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H170" s="1">
         <v>1</v>
       </c>
       <c r="I170" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="171">
@@ -5398,19 +5410,19 @@
         <v>1</v>
       </c>
       <c r="B171" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C171" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D171" t="s">
         <v>110</v>
       </c>
       <c r="E171" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F171" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G171" s="1">
         <v>3</v>
@@ -5419,85 +5431,85 @@
         <v>1</v>
       </c>
       <c r="I171" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B172" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C172" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D172" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E172" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F172" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G172" s="1">
         <v>3</v>
       </c>
       <c r="H172" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I172" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B173" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C173" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D173" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E173" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F173" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G173" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H173" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I173" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B174" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C174" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D174" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E174" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F174" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G174" s="1">
         <v>2</v>
@@ -5506,7 +5518,7 @@
         <v>1</v>
       </c>
       <c r="I174" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="175">
@@ -5514,16 +5526,16 @@
         <v>1</v>
       </c>
       <c r="B175" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C175" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D175" t="s">
         <v>110</v>
       </c>
       <c r="E175" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F175" s="1">
         <v>5</v>
@@ -5535,27 +5547,27 @@
         <v>1</v>
       </c>
       <c r="I175" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B176" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C176" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D176" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E176" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F176" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G176" s="1">
         <v>2</v>
@@ -5564,27 +5576,27 @@
         <v>1</v>
       </c>
       <c r="I176" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B177" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C177" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D177" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E177" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F177" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G177" s="1">
         <v>2</v>
@@ -5593,56 +5605,56 @@
         <v>1</v>
       </c>
       <c r="I177" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C178" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D178" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="E178" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F178" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G178" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H178" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I178" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B179" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C179" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D179" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E179" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F179" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G179" s="1">
         <v>3</v>
@@ -5651,27 +5663,27 @@
         <v>2</v>
       </c>
       <c r="I179" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B180" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C180" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D180" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E180" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F180" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G180" s="1">
         <v>3</v>
@@ -5680,36 +5692,36 @@
         <v>2</v>
       </c>
       <c r="I180" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B181" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C181" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D181" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E181" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F181" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G181" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H181" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I181" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="182">
@@ -5717,16 +5729,16 @@
         <v>4</v>
       </c>
       <c r="B182" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C182" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D182" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E182" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F182" s="1">
         <v>5</v>
@@ -5738,36 +5750,36 @@
         <v>1</v>
       </c>
       <c r="I182" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B183" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C183" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D183" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E183" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F183" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G183" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H183" s="1">
         <v>1</v>
       </c>
       <c r="I183" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="184">
@@ -5775,57 +5787,57 @@
         <v>1</v>
       </c>
       <c r="B184" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C184" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D184" t="s">
         <v>110</v>
       </c>
       <c r="E184" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F184" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G184" s="1">
         <v>3</v>
       </c>
       <c r="H184" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I184" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C185" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D185" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E185" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F185" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G185" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H185" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I185" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="186">
@@ -5833,28 +5845,28 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C186" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D186" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E186" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F186" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G186" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H186" s="1">
         <v>1</v>
       </c>
       <c r="I186" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="187">
@@ -5862,57 +5874,57 @@
         <v>2</v>
       </c>
       <c r="B187" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C187" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D187" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E187" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F187" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G187" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H187" s="1">
         <v>1</v>
       </c>
       <c r="I187" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B188" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C188" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D188" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E188" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F188" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G188" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H188" s="1">
         <v>1</v>
       </c>
       <c r="I188" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="189">
@@ -5920,16 +5932,16 @@
         <v>1</v>
       </c>
       <c r="B189" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C189" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D189" t="s">
         <v>110</v>
       </c>
       <c r="E189" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F189" s="1">
         <v>6</v>
@@ -5941,53 +5953,53 @@
         <v>1</v>
       </c>
       <c r="I189" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B190" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C190" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D190" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E190" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F190" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G190" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H190" s="1">
         <v>1</v>
       </c>
       <c r="I190" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B191" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C191" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D191" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E191" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F191" s="1">
         <v>3</v>
@@ -5999,7 +6011,7 @@
         <v>1</v>
       </c>
       <c r="I191" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="192">
@@ -6007,19 +6019,19 @@
         <v>1</v>
       </c>
       <c r="B192" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C192" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D192" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E192" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F192" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G192" s="1">
         <v>2</v>
@@ -6028,7 +6040,7 @@
         <v>1</v>
       </c>
       <c r="I192" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="193">
@@ -6036,57 +6048,57 @@
         <v>1</v>
       </c>
       <c r="B193" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C193" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D193" t="s">
         <v>110</v>
       </c>
       <c r="E193" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F193" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G193" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H193" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I193" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B194" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C194" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D194" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E194" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F194" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G194" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H194" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I194" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="195">
@@ -6094,16 +6106,16 @@
         <v>2</v>
       </c>
       <c r="B195" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C195" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D195" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E195" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F195" s="1">
         <v>3</v>
@@ -6115,56 +6127,56 @@
         <v>1</v>
       </c>
       <c r="I195" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B196" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C196" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D196" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E196" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F196" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G196" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H196" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I196" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B197" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C197" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D197" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E197" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F197" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G197" s="1">
         <v>3</v>
@@ -6173,36 +6185,36 @@
         <v>2</v>
       </c>
       <c r="I197" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B198" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C198" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D198" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E198" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F198" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G198" s="1">
         <v>3</v>
       </c>
       <c r="H198" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I198" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="199">
@@ -6210,16 +6222,16 @@
         <v>1</v>
       </c>
       <c r="B199" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C199" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D199" t="s">
         <v>110</v>
       </c>
       <c r="E199" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F199" s="1">
         <v>9</v>
@@ -6231,94 +6243,94 @@
         <v>1</v>
       </c>
       <c r="I199" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B200" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C200" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D200" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E200" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F200" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G200" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H200" s="1">
         <v>1</v>
       </c>
       <c r="I200" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B201" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C201" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D201" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E201" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F201" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G201" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H201" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I201" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B202" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C202" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D202" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="E202" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F202" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G202" s="1">
         <v>3</v>
       </c>
       <c r="H202" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I202" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="203">
@@ -6326,16 +6338,16 @@
         <v>1</v>
       </c>
       <c r="B203" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C203" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D203" t="s">
         <v>110</v>
       </c>
       <c r="E203" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F203" s="1">
         <v>8</v>
@@ -6344,97 +6356,97 @@
         <v>3</v>
       </c>
       <c r="H203" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I203" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B204" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C204" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D204" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E204" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F204" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G204" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H204" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I204" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B205" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C205" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D205" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E205" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F205" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G205" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H205" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I205" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B206" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C206" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D206" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E206" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F206" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G206" s="1">
         <v>3</v>
       </c>
       <c r="H206" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I206" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="207">
@@ -6442,16 +6454,16 @@
         <v>1</v>
       </c>
       <c r="B207" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C207" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D207" t="s">
         <v>110</v>
       </c>
       <c r="E207" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F207" s="1">
         <v>9</v>
@@ -6460,30 +6472,30 @@
         <v>3</v>
       </c>
       <c r="H207" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I207" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B208" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C208" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D208" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E208" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F208" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G208" s="1">
         <v>3</v>
@@ -6492,7 +6504,7 @@
         <v>2</v>
       </c>
       <c r="I208" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="209">
@@ -6500,16 +6512,16 @@
         <v>2</v>
       </c>
       <c r="B209" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C209" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D209" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E209" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F209" s="1">
         <v>8</v>
@@ -6521,27 +6533,27 @@
         <v>2</v>
       </c>
       <c r="I209" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B210" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C210" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D210" t="s">
         <v>112</v>
       </c>
       <c r="E210" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F210" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G210" s="1">
         <v>3</v>
@@ -6550,24 +6562,24 @@
         <v>2</v>
       </c>
       <c r="I210" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B211" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C211" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D211" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E211" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F211" s="1">
         <v>7</v>
@@ -6579,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="I211" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="212">
@@ -6587,28 +6599,28 @@
         <v>1</v>
       </c>
       <c r="B212" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C212" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D212" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E212" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F212" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G212" s="1">
         <v>3</v>
       </c>
       <c r="H212" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I212" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="213">
@@ -6616,19 +6628,19 @@
         <v>1</v>
       </c>
       <c r="B213" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C213" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D213" t="s">
         <v>110</v>
       </c>
       <c r="E213" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F213" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G213" s="1">
         <v>3</v>
@@ -6637,94 +6649,94 @@
         <v>1</v>
       </c>
       <c r="I213" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B214" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C214" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D214" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E214" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F214" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G214" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H214" s="1">
         <v>1</v>
       </c>
       <c r="I214" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B215" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C215" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D215" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E215" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F215" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G215" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H215" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I215" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B216" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C216" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D216" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="E216" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F216" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G216" s="1">
         <v>3</v>
       </c>
       <c r="H216" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I216" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="217">
@@ -6732,19 +6744,19 @@
         <v>1</v>
       </c>
       <c r="B217" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C217" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D217" t="s">
         <v>110</v>
       </c>
       <c r="E217" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F217" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G217" s="1">
         <v>3</v>
@@ -6753,36 +6765,36 @@
         <v>1</v>
       </c>
       <c r="I217" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B218" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C218" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D218" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E218" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F218" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G218" s="1">
         <v>3</v>
       </c>
       <c r="H218" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I218" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="219">
@@ -6790,16 +6802,16 @@
         <v>2</v>
       </c>
       <c r="B219" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C219" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D219" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E219" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F219" s="1">
         <v>6</v>
@@ -6811,123 +6823,123 @@
         <v>2</v>
       </c>
       <c r="I219" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B220" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C220" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D220" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E220" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F220" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G220" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H220" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I220" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B221" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C221" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D221" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E221" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F221" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G221" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H221" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I221" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B222" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C222" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D222" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E222" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F222" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G222" s="1">
         <v>3</v>
       </c>
       <c r="H222" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I222" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B223" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C223" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D223" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E223" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F223" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G223" s="1">
         <v>3</v>
       </c>
       <c r="H223" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I223" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="224">
@@ -6935,28 +6947,28 @@
         <v>2</v>
       </c>
       <c r="B224" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C224" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D224" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E224" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F224" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G224" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H224" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I224" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="225">
@@ -6964,77 +6976,77 @@
         <v>2</v>
       </c>
       <c r="B225" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C225" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D225" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E225" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F225" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G225" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H225" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I225" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B226" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C226" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D226" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="E226" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F226" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G226" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H226" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I226" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B227" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C227" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D227" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E227" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F227" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G227" s="1">
         <v>2</v>
@@ -7043,24 +7055,24 @@
         <v>1</v>
       </c>
       <c r="I227" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B228" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C228" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D228" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E228" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F228" s="1">
         <v>3</v>
@@ -7072,36 +7084,36 @@
         <v>1</v>
       </c>
       <c r="I228" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B229" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C229" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D229" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E229" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F229" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G229" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H229" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I229" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="230">
@@ -7109,16 +7121,16 @@
         <v>1</v>
       </c>
       <c r="B230" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C230" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D230" t="s">
         <v>110</v>
       </c>
       <c r="E230" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F230" s="1">
         <v>8</v>
@@ -7127,39 +7139,39 @@
         <v>3</v>
       </c>
       <c r="H230" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I230" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B231" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C231" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D231" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E231" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F231" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G231" s="1">
         <v>3</v>
       </c>
       <c r="H231" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I231" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="232">
@@ -7167,16 +7179,16 @@
         <v>2</v>
       </c>
       <c r="B232" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C232" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D232" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E232" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F232" s="1">
         <v>9</v>
@@ -7188,27 +7200,27 @@
         <v>2</v>
       </c>
       <c r="I232" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B233" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C233" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D233" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E233" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F233" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G233" s="1">
         <v>3</v>
@@ -7217,24 +7229,24 @@
         <v>2</v>
       </c>
       <c r="I233" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B234" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C234" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D234" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E234" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F234" s="1">
         <v>6</v>
@@ -7246,27 +7258,27 @@
         <v>2</v>
       </c>
       <c r="I234" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B235" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C235" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D235" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E235" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F235" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G235" s="1">
         <v>3</v>
@@ -7275,82 +7287,82 @@
         <v>2</v>
       </c>
       <c r="I235" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B236" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C236" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D236" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E236" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F236" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G236" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H236" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I236" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B237" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C237" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D237" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E237" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F237" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G237" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H237" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I237" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B238" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C238" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D238" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E238" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F238" s="1">
         <v>9</v>
@@ -7359,10 +7371,10 @@
         <v>3</v>
       </c>
       <c r="H238" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I238" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="239">
@@ -7370,16 +7382,16 @@
         <v>1</v>
       </c>
       <c r="B239" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C239" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D239" t="s">
         <v>110</v>
       </c>
       <c r="E239" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F239" s="1">
         <v>9</v>
@@ -7391,7 +7403,7 @@
         <v>1</v>
       </c>
       <c r="I239" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="240">
@@ -7399,57 +7411,57 @@
         <v>1</v>
       </c>
       <c r="B240" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C240" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D240" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E240" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F240" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G240" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H240" s="1">
         <v>1</v>
       </c>
       <c r="I240" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B241" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C241" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D241" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E241" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F241" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G241" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H241" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I241" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="242">
@@ -7457,19 +7469,19 @@
         <v>2</v>
       </c>
       <c r="B242" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C242" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D242" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E242" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F242" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G242" s="1">
         <v>3</v>
@@ -7478,85 +7490,85 @@
         <v>2</v>
       </c>
       <c r="I242" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B243" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C243" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D243" t="s">
         <v>112</v>
       </c>
       <c r="E243" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F243" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G243" s="1">
         <v>3</v>
       </c>
       <c r="H243" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I243" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B244" t="s">
         <v>17</v>
       </c>
       <c r="C244" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D244" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E244" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F244" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G244" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H244" s="1">
         <v>1</v>
       </c>
       <c r="I244" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B245" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C245" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D245" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E245" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F245" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G245" s="1">
         <v>2</v>
@@ -7565,7 +7577,7 @@
         <v>1</v>
       </c>
       <c r="I245" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="246">
@@ -7573,19 +7585,19 @@
         <v>2</v>
       </c>
       <c r="B246" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C246" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D246" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E246" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F246" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G246" s="1">
         <v>2</v>
@@ -7594,27 +7606,27 @@
         <v>1</v>
       </c>
       <c r="I246" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B247" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C247" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D247" t="s">
         <v>112</v>
       </c>
       <c r="E247" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F247" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G247" s="1">
         <v>2</v>
@@ -7623,24 +7635,24 @@
         <v>1</v>
       </c>
       <c r="I247" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B248" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C248" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D248" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E248" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F248" s="1">
         <v>3</v>
@@ -7652,24 +7664,24 @@
         <v>1</v>
       </c>
       <c r="I248" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B249" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C249" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D249" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E249" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F249" s="1">
         <v>3</v>
@@ -7681,7 +7693,7 @@
         <v>1</v>
       </c>
       <c r="I249" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="250">
@@ -7689,16 +7701,16 @@
         <v>2</v>
       </c>
       <c r="B250" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C250" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D250" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E250" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F250" s="1">
         <v>3</v>
@@ -7710,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="I250" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="251">
@@ -7718,16 +7730,16 @@
         <v>2</v>
       </c>
       <c r="B251" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C251" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D251" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E251" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F251" s="1">
         <v>3</v>
@@ -7739,7 +7751,7 @@
         <v>1</v>
       </c>
       <c r="I251" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="252">
@@ -7747,28 +7759,28 @@
         <v>2</v>
       </c>
       <c r="B252" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C252" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D252" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E252" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F252" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G252" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H252" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I252" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="253">
@@ -7776,28 +7788,28 @@
         <v>2</v>
       </c>
       <c r="B253" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C253" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D253" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E253" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F253" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G253" s="1">
         <v>3</v>
       </c>
       <c r="H253" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I253" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="254">
@@ -7805,16 +7817,16 @@
         <v>2</v>
       </c>
       <c r="B254" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C254" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D254" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E254" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F254" s="1">
         <v>6</v>
@@ -7826,53 +7838,53 @@
         <v>1</v>
       </c>
       <c r="I254" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B255" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C255" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D255" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E255" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F255" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G255" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H255" s="1">
         <v>1</v>
       </c>
       <c r="I255" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B256" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C256" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D256" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E256" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F256" s="1">
         <v>3</v>
@@ -7884,7 +7896,7 @@
         <v>1</v>
       </c>
       <c r="I256" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="257">
@@ -7892,16 +7904,16 @@
         <v>2</v>
       </c>
       <c r="B257" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C257" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D257" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E257" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F257" s="1">
         <v>3</v>
@@ -7913,24 +7925,24 @@
         <v>1</v>
       </c>
       <c r="I257" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B258" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C258" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D258" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E258" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F258" s="1">
         <v>3</v>
@@ -7942,24 +7954,24 @@
         <v>1</v>
       </c>
       <c r="I258" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B259" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C259" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D259" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E259" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F259" s="1">
         <v>3</v>
@@ -7971,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="I259" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="260">
@@ -7979,16 +7991,16 @@
         <v>2</v>
       </c>
       <c r="B260" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C260" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D260" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E260" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F260" s="1">
         <v>3</v>
@@ -8000,7 +8012,7 @@
         <v>1</v>
       </c>
       <c r="I260" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="261">
@@ -8008,48 +8020,48 @@
         <v>2</v>
       </c>
       <c r="B261" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C261" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D261" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E261" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F261" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G261" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H261" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I261" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B262" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C262" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D262" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E262" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F262" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G262" s="1">
         <v>3</v>
@@ -8058,27 +8070,27 @@
         <v>2</v>
       </c>
       <c r="I262" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B263" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C263" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="D263" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E263" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F263" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G263" s="1">
         <v>3</v>
@@ -8087,7 +8099,7 @@
         <v>2</v>
       </c>
       <c r="I263" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="264">
@@ -8095,115 +8107,202 @@
         <v>2</v>
       </c>
       <c r="B264" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C264" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D264" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E264" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F264" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G264" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H264" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I264" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B265" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C265" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D265" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E265" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F265" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G265" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H265" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I265" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B266" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C266" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D266" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E266" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F266" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G266" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H266" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I266" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B267" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C267" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D267" t="s">
         <v>112</v>
       </c>
       <c r="E267" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F267" s="1">
+        <v>3</v>
+      </c>
+      <c r="G267" s="1">
+        <v>2</v>
+      </c>
+      <c r="H267" s="1">
+        <v>1</v>
+      </c>
+      <c r="I267" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>3</v>
+      </c>
+      <c r="B268" t="s">
+        <v>18</v>
+      </c>
+      <c r="C268" t="s">
+        <v>90</v>
+      </c>
+      <c r="D268" t="s">
+        <v>115</v>
+      </c>
+      <c r="E268" t="s">
+        <v>131</v>
+      </c>
+      <c r="F268" s="1">
         <v>8</v>
       </c>
-      <c r="G267" s="1">
-        <v>3</v>
-      </c>
-      <c r="H267" s="1">
-        <v>2</v>
-      </c>
-      <c r="I267" t="s">
-        <v>133</v>
+      <c r="G268" s="1">
+        <v>3</v>
+      </c>
+      <c r="H268" s="1">
+        <v>2</v>
+      </c>
+      <c r="I268" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>8</v>
+      </c>
+      <c r="B269" t="s">
+        <v>18</v>
+      </c>
+      <c r="C269" t="s">
+        <v>108</v>
+      </c>
+      <c r="D269" t="s">
+        <v>114</v>
+      </c>
+      <c r="E269" t="s">
+        <v>131</v>
+      </c>
+      <c r="F269" s="1">
+        <v>6</v>
+      </c>
+      <c r="G269" s="1">
+        <v>2</v>
+      </c>
+      <c r="H269" s="1">
+        <v>1</v>
+      </c>
+      <c r="I269" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>12</v>
+      </c>
+      <c r="B270" t="s">
+        <v>18</v>
+      </c>
+      <c r="C270" t="s">
+        <v>108</v>
+      </c>
+      <c r="D270" t="s">
+        <v>114</v>
+      </c>
+      <c r="E270" t="s">
+        <v>131</v>
+      </c>
+      <c r="F270" s="1">
+        <v>6</v>
+      </c>
+      <c r="G270" s="1">
+        <v>2</v>
+      </c>
+      <c r="H270" s="1">
+        <v>1</v>
+      </c>
+      <c r="I270" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
